--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MASSACHUSETTS_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MASSACHUSETTS_2014.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C81">
